--- a/assets/constructions/examples/ctd_tge_blade_holder.xlsx
+++ b/assets/constructions/examples/ctd_tge_blade_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,41 +564,69 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SMBB2526</t>
+          <t>32251221200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WGC</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LIK_SPB_ 26-S</t>
+          <t>WID_WGC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ISO_5610:25X23</t>
+          <t>ISO_5610:19.05X19.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LIKON_BLADE_SPB:26</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>WIDIA_BLADE_WGC:19</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
@@ -613,27 +641,25 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>23</v>
+        <v>19.05</v>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>26</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>86</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="W2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="X2" t="b">
         <v>0</v>
@@ -644,44 +670,50 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Токарный каталог</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VBA 075-26</t>
+          <t>12251222500</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>WGC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VAR_VBA26</t>
+          <t>WID_WGC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ISO_5610:19.05X20</t>
+          <t>ISO_5610:25X20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS_BLADE_H:26</t>
+          <t>WIDIA_BLADE_WGC:32</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -707,21 +739,23 @@
         <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10</v>
+      </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>26</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>37</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50</v>
+      </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
@@ -731,14 +765,20 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Токарный каталог</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMBB3232</t>
+          <t>SMBB2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -749,7 +789,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LIK_SPB_ 32-S</t>
+          <t>LIK_SPB_ 26-S</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -759,12 +799,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ISO_5610:32X30</t>
+          <t>ISO_5610:20X19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LIKON_BLADE_SPB:32</t>
+          <t>LIKON_BLADE_SPB:26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -783,27 +823,27 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="P4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="W4" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
@@ -817,49 +857,43 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12251234000</t>
+          <t>CPTS 1916</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WGC</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>WID_WGC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
+          <t>CPTS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ISO_5610:40X40</t>
+          <t>ISO_5610:16X16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WIDIA_BLADE_WGC:52.5</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+          <t>PALB_BLADE_BLS:19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
@@ -874,69 +908,93 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>22</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>19</v>
+      </c>
       <c r="T5" t="n">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>65</v>
-      </c>
-      <c r="W5" t="n">
-        <v>82</v>
-      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>0</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Токарный каталог</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>251.06</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>23080.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CPTS 3220</t>
+          <t>12251222000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPTS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>WGC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WID_WGC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WIDIA</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ISO_5610:20X20</t>
+          <t>ISO_5610:20X18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PALB_BLADE_BLS:32|PALB_BLADE_GPNC:32</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>WIDIA_BLADE_WGC:26</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
@@ -951,36 +1009,44 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>32</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>100</v>
       </c>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>40</v>
+      </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022/ palbit основной каталог.pdf</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Токарный каталог</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
